--- a/example_project/Analysis/MG_motility/all_pixel_areas.xlsx
+++ b/example_project/Analysis/MG_motility/all_pixel_areas.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,41 +413,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>project tag</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>tag folders</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
         <is>
           <t>projection center</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>source image</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>t_i</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>cell area in pixel rel to stack 0</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>cell area in pixel total</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>total fov area in pixel</t>
         </is>
@@ -478,19 +476,29 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>projection_center_23</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+          <t>TP000/registered</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>projection_center_28</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ID240103_P17_1/TP000/registered/all stacks 4D reg.tif</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>100</v>
       </c>
-      <c r="F2" t="n">
-        <v>654189</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
+        <v>810261</v>
+      </c>
+      <c r="I2" t="n">
         <v>1644050</v>
       </c>
     </row>
@@ -507,19 +515,29 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>projection_center_23</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+          <t>TP000/registered</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>projection_center_28</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ID240103_P17_1/TP000/registered/all stacks 4D reg.tif</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="n">
-        <v>98.50349058146804</v>
-      </c>
-      <c r="F3" t="n">
-        <v>644399</v>
-      </c>
       <c r="G3" t="n">
+        <v>99.91237391408447</v>
+      </c>
+      <c r="H3" t="n">
+        <v>809551</v>
+      </c>
+      <c r="I3" t="n">
         <v>1644050</v>
       </c>
     </row>
@@ -536,19 +554,29 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>projection_center_23</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+          <t>TP000/registered</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>projection_center_28</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ID240103_P17_1/TP000/registered/all stacks 4D reg.tif</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>2</v>
       </c>
-      <c r="E4" t="n">
-        <v>98.40351947220145</v>
-      </c>
-      <c r="F4" t="n">
-        <v>643745</v>
-      </c>
       <c r="G4" t="n">
+        <v>99.98580704242214</v>
+      </c>
+      <c r="H4" t="n">
+        <v>810146</v>
+      </c>
+      <c r="I4" t="n">
         <v>1644050</v>
       </c>
     </row>
@@ -565,19 +593,29 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>projection_center_23</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+          <t>TP000/registered</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>projection_center_28</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ID240103_P17_1/TP000/registered/all stacks 4D reg.tif</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>3</v>
       </c>
-      <c r="E5" t="n">
-        <v>91.76766958784083</v>
-      </c>
-      <c r="F5" t="n">
-        <v>600334</v>
-      </c>
       <c r="G5" t="n">
+        <v>97.92708769149694</v>
+      </c>
+      <c r="H5" t="n">
+        <v>793465</v>
+      </c>
+      <c r="I5" t="n">
         <v>1644050</v>
       </c>
     </row>
@@ -594,19 +632,29 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>projection_center_23</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+          <t>TP000/registered</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>projection_center_28</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ID240103_P17_1/TP000/registered/all stacks 4D reg.tif</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>4</v>
       </c>
-      <c r="E6" t="n">
-        <v>92.73803136402476</v>
-      </c>
-      <c r="F6" t="n">
-        <v>606682</v>
-      </c>
       <c r="G6" t="n">
+        <v>97.65951958689854</v>
+      </c>
+      <c r="H6" t="n">
+        <v>791297</v>
+      </c>
+      <c r="I6" t="n">
         <v>1644050</v>
       </c>
     </row>
@@ -623,19 +671,29 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>projection_center_23</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+          <t>TP000/registered</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>projection_center_28</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ID240103_P17_1/TP000/registered/all stacks 4D reg.tif</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="n">
-        <v>90.73906776176304</v>
-      </c>
-      <c r="F7" t="n">
-        <v>593605</v>
-      </c>
       <c r="G7" t="n">
+        <v>97.66963978273667</v>
+      </c>
+      <c r="H7" t="n">
+        <v>791379</v>
+      </c>
+      <c r="I7" t="n">
         <v>1644050</v>
       </c>
     </row>
@@ -652,19 +710,29 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>projection_center_23</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+          <t>TP000/registered</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>projection_center_28</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ID240103_P17_1/TP000/registered/all stacks 4D reg.tif</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>6</v>
       </c>
-      <c r="E8" t="n">
-        <v>96.79771442197897</v>
-      </c>
-      <c r="F8" t="n">
-        <v>633240</v>
-      </c>
       <c r="G8" t="n">
+        <v>98.89776257280062</v>
+      </c>
+      <c r="H8" t="n">
+        <v>801330</v>
+      </c>
+      <c r="I8" t="n">
         <v>1644050</v>
       </c>
     </row>
@@ -681,26 +749,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>projection_center_23</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+          <t>TP000/registered</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>projection_center_28</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ID240103_P17_1/TP000/registered/all stacks 4D reg.tif</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>7</v>
       </c>
-      <c r="E9" t="n">
-        <v>96.35029020665282</v>
-      </c>
-      <c r="F9" t="n">
-        <v>630313</v>
-      </c>
       <c r="G9" t="n">
+        <v>98.48320479450449</v>
+      </c>
+      <c r="H9" t="n">
+        <v>797971</v>
+      </c>
+      <c r="I9" t="n">
         <v>1644050</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ID240103_P17_1</t>
+          <t>ID240321_P17_3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -710,26 +788,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>projection_center_28</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+          <t>TP000/registered</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>projection_center_28</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ID240321_P17_3/TP000/registered/all stacks 4D reg.tif</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="n">
+      <c r="G10" t="n">
         <v>100</v>
       </c>
-      <c r="F10" t="n">
-        <v>810261</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1644050</v>
+      <c r="H10" t="n">
+        <v>794681</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1603470</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ID240103_P17_1</t>
+          <t>ID240321_P17_3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -739,26 +827,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>projection_center_28</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+          <t>TP000/registered</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>projection_center_28</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ID240321_P17_3/TP000/registered/all stacks 4D reg.tif</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>1</v>
       </c>
-      <c r="E11" t="n">
-        <v>99.91237391408447</v>
-      </c>
-      <c r="F11" t="n">
-        <v>809551</v>
-      </c>
       <c r="G11" t="n">
-        <v>1644050</v>
+        <v>99.67030796004939</v>
+      </c>
+      <c r="H11" t="n">
+        <v>792061</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1603470</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ID240103_P17_1</t>
+          <t>ID240321_P17_3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -768,26 +866,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>projection_center_28</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
+          <t>TP000/registered</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>projection_center_28</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ID240321_P17_3/TP000/registered/all stacks 4D reg.tif</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>2</v>
       </c>
-      <c r="E12" t="n">
-        <v>99.98580704242214</v>
-      </c>
-      <c r="F12" t="n">
-        <v>810146</v>
-      </c>
       <c r="G12" t="n">
-        <v>1644050</v>
+        <v>100.3931137148113</v>
+      </c>
+      <c r="H12" t="n">
+        <v>797805</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1603470</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ID240103_P17_1</t>
+          <t>ID240321_P17_3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -797,26 +905,36 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>projection_center_28</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
+          <t>TP000/registered</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>projection_center_28</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ID240321_P17_3/TP000/registered/all stacks 4D reg.tif</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>3</v>
       </c>
-      <c r="E13" t="n">
-        <v>97.92708769149694</v>
-      </c>
-      <c r="F13" t="n">
-        <v>793465</v>
-      </c>
       <c r="G13" t="n">
-        <v>1644050</v>
+        <v>99.74870419703001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>792684</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1603470</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ID240103_P17_1</t>
+          <t>ID240321_P17_3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -826,26 +944,36 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>projection_center_28</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
+          <t>TP000/registered</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>projection_center_28</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ID240321_P17_3/TP000/registered/all stacks 4D reg.tif</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>4</v>
       </c>
-      <c r="E14" t="n">
-        <v>97.65951958689854</v>
-      </c>
-      <c r="F14" t="n">
-        <v>791297</v>
-      </c>
       <c r="G14" t="n">
-        <v>1644050</v>
+        <v>98.34839388383514</v>
+      </c>
+      <c r="H14" t="n">
+        <v>781556</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1603470</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ID240103_P17_1</t>
+          <t>ID240321_P17_3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -855,26 +983,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>projection_center_28</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
+          <t>TP000/registered</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>projection_center_28</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ID240321_P17_3/TP000/registered/all stacks 4D reg.tif</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>5</v>
       </c>
-      <c r="E15" t="n">
-        <v>97.66963978273667</v>
-      </c>
-      <c r="F15" t="n">
-        <v>791379</v>
-      </c>
       <c r="G15" t="n">
-        <v>1644050</v>
+        <v>98.01190666443516</v>
+      </c>
+      <c r="H15" t="n">
+        <v>778882</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1603470</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ID240103_P17_1</t>
+          <t>ID240321_P17_3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -884,26 +1022,36 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>projection_center_28</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
+          <t>TP000/registered</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>projection_center_28</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ID240321_P17_3/TP000/registered/all stacks 4D reg.tif</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>6</v>
       </c>
-      <c r="E16" t="n">
-        <v>98.89776257280062</v>
-      </c>
-      <c r="F16" t="n">
-        <v>801330</v>
-      </c>
       <c r="G16" t="n">
-        <v>1644050</v>
+        <v>98.54809665765256</v>
+      </c>
+      <c r="H16" t="n">
+        <v>783143</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1603470</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ID240103_P17_1</t>
+          <t>ID240321_P17_3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -913,251 +1061,29 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>projection_center_28</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
+          <t>TP000/registered</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>projection_center_28</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ID240321_P17_3/TP000/registered/all stacks 4D reg.tif</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
         <v>7</v>
       </c>
-      <c r="E17" t="n">
-        <v>98.48320479450449</v>
-      </c>
-      <c r="F17" t="n">
-        <v>797971</v>
-      </c>
       <c r="G17" t="n">
-        <v>1644050</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ID240321_P17_3</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>TP000</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>projection_center_28</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>100</v>
-      </c>
-      <c r="F18" t="n">
-        <v>794681</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1603470</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>ID240321_P17_3</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>TP000</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>projection_center_28</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" t="n">
-        <v>99.67030796004939</v>
-      </c>
-      <c r="F19" t="n">
-        <v>792061</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1603470</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>ID240321_P17_3</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>TP000</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>projection_center_28</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" t="n">
-        <v>100.3931137148113</v>
-      </c>
-      <c r="F20" t="n">
-        <v>797805</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1603470</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>ID240321_P17_3</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>TP000</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>projection_center_28</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>3</v>
-      </c>
-      <c r="E21" t="n">
-        <v>99.74870419703001</v>
-      </c>
-      <c r="F21" t="n">
-        <v>792684</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1603470</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>ID240321_P17_3</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>TP000</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>projection_center_28</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>4</v>
-      </c>
-      <c r="E22" t="n">
-        <v>98.34839388383514</v>
-      </c>
-      <c r="F22" t="n">
-        <v>781556</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1603470</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>ID240321_P17_3</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>TP000</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>projection_center_28</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>5</v>
-      </c>
-      <c r="E23" t="n">
-        <v>98.01190666443516</v>
-      </c>
-      <c r="F23" t="n">
-        <v>778882</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1603470</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>ID240321_P17_3</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>TP000</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>projection_center_28</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>6</v>
-      </c>
-      <c r="E24" t="n">
-        <v>98.54809665765256</v>
-      </c>
-      <c r="F24" t="n">
-        <v>783143</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1603470</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>ID240321_P17_3</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>TP000</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>projection_center_28</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>7</v>
-      </c>
-      <c r="E25" t="n">
         <v>98.44100966299685</v>
       </c>
-      <c r="F25" t="n">
+      <c r="H17" t="n">
         <v>782292</v>
       </c>
-      <c r="G25" t="n">
+      <c r="I17" t="n">
         <v>1603470</v>
       </c>
     </row>
